--- a/data_tables/balance_enchant_text.xlsx
+++ b/data_tables/balance_enchant_text.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Factor with the piece over the factor without it: 1.5 / 1.25 one to four levels below the enemy, 4 / 3 five to nine below, 6 / 5 ten to nineteen below; 10 / 10 from twenty below, where the piece adds nothing</t>
+          <t>Factor with the piece over the factor without it: 1.5 / 1.15 one to four levels below the enemy (X01 is 1.15 since 2026-10-13), 4 / 3 five to nine below, 6 / 5 ten to nineteen below; 10 / 10 from twenty below, where the piece adds nothing</t>
         </is>
       </c>
     </row>
